--- a/AAII_Financials/Quarterly/GPC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GPC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>GPC</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6537000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6264900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6009400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6260200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6164400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5866100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5770200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5970200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5962600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5783600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5585900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5824600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5915000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5765100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5523700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5675300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5602400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5294600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4803200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4818800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4783700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4464700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4251600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4370100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3823200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4092500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4279900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4525300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4457900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4259100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4603800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4722900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4822100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4586300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4207100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4095900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4100200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3905600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3780100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3941700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4061000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3926000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3748000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3918800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3840000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3692400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3638400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3771800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3774800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3709000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3552600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3715400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3780300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3751700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3550000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3695600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3641600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3468700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3109800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3108100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3094600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2923900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2803500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2842000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2532700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2704300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2800900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3020100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2975200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2866300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3061600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3238700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3300500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3150500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2923000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2869000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2860500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2749900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2649000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2743100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2476000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2339000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2261400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2341400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2324400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2173700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2131800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2198400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2187800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2074700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2033300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2109200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2134700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2013400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1973700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1979700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1960800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1825900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1693400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1710700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1689100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1540800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1448100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1528100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1290500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1388200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1479000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1505200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1482700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1392800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1542200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1484200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1521600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1435800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1284100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1226900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1239700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1155700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1131100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1198600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,40 +1496,43 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>92600</v>
+      </c>
+      <c r="E14" s="3">
         <v>75300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1070600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>66800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>45700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>68800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>125400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>45300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>62000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>83000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1523,11 +1543,11 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1535,8 +1555,8 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1548,37 +1568,37 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3">
         <v>11000</v>
       </c>
       <c r="AA14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AB14" s="3">
         <v>530600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>142800</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>134700</v>
+      </c>
+      <c r="E15" s="3">
         <v>131000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>172100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>127500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>123000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>115400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>112100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>106000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>99200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>90600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>88600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>83900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>90900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>87200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>88000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>86600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>85900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>87400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>72600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>72100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>74000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>72300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>69800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>69100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>66700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>67300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>70300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>65700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>62700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>58600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>63700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>61100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>58500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>58400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>50100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>40300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>39200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>38100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>39200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>37700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6108000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5903400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5717900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5857700</v>
       </c>
-      <c r="G17" s="3">
-        <v>5740500</v>
-      </c>
       <c r="H17" s="3">
+        <v>5741900</v>
+      </c>
+      <c r="I17" s="3">
         <v>5509300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5440300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5587900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5487200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5365500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5154600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5346800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5448500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5343200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5176100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5246700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5094400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4964500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4465100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4523300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4522900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4196300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4016700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4067900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4113000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3923800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4180700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4262600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4170700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4040100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4345200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4424000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4510800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4345300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3974700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3849600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3809200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3668500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3548300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3650400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>428900</v>
+      </c>
+      <c r="E18" s="3">
         <v>361500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>291500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>402500</v>
       </c>
-      <c r="G18" s="3">
-        <v>423900</v>
-      </c>
       <c r="H18" s="3">
+        <v>422600</v>
+      </c>
+      <c r="I18" s="3">
         <v>356800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>329900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>382300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>475400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>418100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>431300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>477800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>466500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>421900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>347600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>428600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>508000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>330100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>338100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>295500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>260800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>268400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>234900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>302200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-289800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>168700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>99200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>262700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>287200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>219000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>258600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>298900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>311300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>241000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>232400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>246300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>291000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>237100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>231800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>291300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>11600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>15500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>19900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>18400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>25000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>35800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>21200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>10800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>12900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>24000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>47600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>18300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>22000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>17900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>15500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>12400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>31100</v>
       </c>
-      <c r="AL20" s="3">
-        <v>0</v>
-      </c>
       <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3">
         <v>13600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>13500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>25600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E21" s="3">
         <v>495600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>458700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>526300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>547500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>473100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>433900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>476700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>569300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>516500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>522700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>564700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>561400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>508500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>440900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>522700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>597700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>432900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>430500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>386100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>359700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>376500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>314100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>392600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-212200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>248800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>193500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>376000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>364800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>277800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>344300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>377900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>385200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>311800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>313500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>286600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>343800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>288700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>296600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>329000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E22" s="3">
         <v>44000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>45700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>40200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>37200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>27800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>15000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>25500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>21000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>22000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>26500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>26300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>26500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>41500</v>
       </c>
-      <c r="AL22" s="3" t="s">
+      <c r="AM22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>7400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>6800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>21100</v>
       </c>
-      <c r="AP22" s="3" t="s">
+      <c r="AQ22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>293800</v>
+      </c>
+      <c r="E23" s="3">
         <v>245400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-829700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>291700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>338600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>251600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>167000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>297600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>386200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>325200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>418800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>465100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>454100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>404400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>337400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>417900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>491600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>325700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>345900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>299000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>269600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>285900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>225500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>297700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-304400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>160600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>101200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>283900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>282200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>192000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>254300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>291700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>300300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>229300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>222000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>246400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>297100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>243800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>236300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>291400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E24" s="3">
         <v>56900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-220200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>65500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>83700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>57200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>33900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>71000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>90700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>76300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>101900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>113900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>109600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>85400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>105600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>119000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>79900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>89900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>70400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>73100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>68100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>53900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>64700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>59100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>38200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>17700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>71600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>72700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>46300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>62300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>71500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>73300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>52700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>62800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>87900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>107200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>83600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>83800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E26" s="3">
         <v>188500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-609500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>226200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>254900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>194400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>133100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>226600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>295500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>248900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>316900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>351200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>344500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>304000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>252000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>312400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>372500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>245800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>256000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>228600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>196500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>217700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>171600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>232900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-363500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>122300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>83500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>212300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>209500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>145700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>192000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>220200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>176600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>159200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>158400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>190000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>160200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>152500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>185300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E27" s="3">
         <v>188500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-609500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>226200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>254900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>194400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>133100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>226600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>295500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>248900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>316900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>351200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>344500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>304000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>252000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>312400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>372500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>245800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>256000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>228600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>196500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>217700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>171600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>232900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-363500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>122300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>83500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>212300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>209500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>145700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>192000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>220200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>176600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>159200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>158400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>190000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>160200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>152500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>185300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3200,14 +3261,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -3219,34 +3280,34 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-200900</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>14200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-74600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>15200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>14900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>14600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-5300</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-51000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E32" s="3">
         <v>3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3600</v>
       </c>
-      <c r="G32" s="3">
-        <v>500</v>
-      </c>
       <c r="H32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-11600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-15500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-19900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-18400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-25000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-35800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-21200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-47600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-18300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-15500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-12400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-31100</v>
       </c>
-      <c r="AL32" s="3">
-        <v>0</v>
-      </c>
       <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3">
         <v>-13600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-13500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-25600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E33" s="3">
         <v>188500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-609500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>226200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>254900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>194400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>133100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>226600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>295500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>248900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>316900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>351200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>344500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>304000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>252000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>312400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>372500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>245800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>256000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>228600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>196500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>217700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>171200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>227500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-564400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>136500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>227500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>224400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>160300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>186700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>220200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>176600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>108200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>158400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>190000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>160200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>152500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>185300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E35" s="3">
         <v>188500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-609500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>226200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>254900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>194400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>133100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>226600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>295500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>248900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>316900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>351200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>344500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>304000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>252000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>312400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>372500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>245800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>256000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>228600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>196500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>217700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>171200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>227500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-564400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>136500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>227500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>224400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>160300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>186700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>220200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>176600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>108200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>158400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>190000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>160200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>152500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>185300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>559100</v>
+      </c>
+      <c r="E41" s="3">
         <v>500000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>477200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>431400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>458000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>420400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>480000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1078100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>555300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1049600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1102000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>654600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>530100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>651200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>653500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>629200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>519100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>610800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>714700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>919100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>987400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1118000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>990200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>900100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>983800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>354500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>277000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>451300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>562600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>356900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>333500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>359100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>355100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>326000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>314900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>210100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>203100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>177900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>242900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>225200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,496 +4553,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3441300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3378300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3278300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3725900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3570500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3467100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3155700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3394300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3417900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3300100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3151900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3220100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2554200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2420800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2188900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2215000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2235500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2137800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1798000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1888300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1900000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1809600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1557000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1952200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1823400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2705200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2635200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2740000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2836900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2741900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2493600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2655900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2669600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2641200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2421600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>5510100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2170000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2084900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1938600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2032500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6287900</v>
+      </c>
+      <c r="E44" s="3">
         <v>6127200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6072000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5873800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5774000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5632900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5514400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5527000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5103600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4736100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4676700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4482800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4512900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4579600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4441600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4300700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4296200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4211500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3889900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3748400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3679100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3600700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3506300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3419400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3351800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3698900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3831200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3718300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3750800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3684600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3609400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3536500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3484900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3772900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3771100</v>
       </c>
-      <c r="AL44" s="3" t="s">
+      <c r="AM44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>3330200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>3287000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>3210300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>3146200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>585700</v>
+      </c>
+      <c r="E45" s="3">
         <v>637100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>587300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>495800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>520000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>584100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>564700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>568400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>558500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>564400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>555000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>45200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1532800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1678300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1475500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1467400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1353800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1226400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1155100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1149900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1060400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1103600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1132500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1234500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1195300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1149100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1034500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1103000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1139100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>999000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1013600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>841600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>805300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>596400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>598100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>644200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>556700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>504600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11065700</v>
+      </c>
+      <c r="E46" s="3">
         <v>10884500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10564700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10667000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10473800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10214400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9852600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10709500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9796700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9806300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9605900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9029900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9083700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9184400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8816700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8823200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8526300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8427400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7756400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7782200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7721600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7678200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7113800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7375300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7291300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7993100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7938600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8058700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8184700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7886400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7575700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7550500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7523400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7581600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7312900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6316600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6301400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>6194100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5948400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5908500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4995,8 +5100,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4170900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4212600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4256600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4062400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3992800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3815900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3720500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3575300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3392400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3029000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2885500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2711100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2583900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2494500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2430700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2315400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2304500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2364800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2288100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2148100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2235000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2209400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2200900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2165900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2131100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2229700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2290800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2167400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2051700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1998300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1027200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>937700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>918600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>931300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>936700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>760200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>740800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>737200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>728100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>688900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4965000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4987700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5044500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4983200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4972200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4826100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4696300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4950200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4677600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4509200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4527600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4392100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4405400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4389900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4400600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4209200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4391500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4469700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3321700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3300700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3384400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3340800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3415700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3279400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3194500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3675600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3862400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3801700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3847200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3642000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3540400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3518500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3499000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3618400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3554400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1713600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1677700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1608500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1574700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1550400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>856800</v>
+      </c>
+      <c r="E52" s="3">
         <v>891800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>929700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>982300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>992400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>960800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1013300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1024200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1002700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>992000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>949500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>888800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>868600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>838700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>847300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1029300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1016000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1011400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>985900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>743900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>744900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>715200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>709800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>654900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>647000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>553000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>553800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>485400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>555900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>543800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>539700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>650400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>625600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>628100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>608400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>703800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>692200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>627100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>608200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>601600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21058300</v>
+      </c>
+      <c r="E54" s="3">
         <v>20976600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20795500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20694900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20431100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19817200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19282700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20259200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18869400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18336500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17968500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17021900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16941600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16907500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16495400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16377100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16238200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16273300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14352100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13974900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14086000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13943500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13440200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13475500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13264000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>14451400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>14645600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>14513200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14639500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14070500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12683000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12657100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12566500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12759400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12412400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9494200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>9412100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9166800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8859400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>8749400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,603 +6145,616 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6279900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6177900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6051900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6100200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5996900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6011300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5923700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6100500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5932000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5725700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5499500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5486400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5570600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5677100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5456600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5531300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5409600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5214500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4804900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4819100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4729200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4479400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4128100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4030300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3745000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4067400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4106200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4195900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4064500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4058200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3995800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4036000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3831300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3773100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3634900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3275200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3303000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3231000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3081100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3099400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1002500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1517000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1691900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1012700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1062700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>813900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>885000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>811000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>853200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>845100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>653700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>354000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>417600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>290300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>252000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>120000</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>48100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>160400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>160500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>206300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>489000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>908900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>624000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>622100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1011300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1032400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>711100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>450500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>686400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>751600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>695000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>595000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>580000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>475000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>325000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>475000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2265700</v>
+      </c>
+      <c r="E59" s="3">
         <v>2261700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2027900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2270200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2153500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2060000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1702300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2211900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1981200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2068700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1660800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1960000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1911600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1950100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1977500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1962200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1870200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1915000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1776600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1718200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1743900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1696600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1605500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1740000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1734700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1605000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1663900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1554800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1422300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1454700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1193800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1174700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1139200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1232700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1144200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>932500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>918200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>873800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>838000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>827100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9548100</v>
+      </c>
+      <c r="E60" s="3">
         <v>9956500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9787700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9383100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9213100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8885200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8525400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9123400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8766400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8639500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7827100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7800400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7899800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7917500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7686100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7495100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7293900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7249500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6581600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6537300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6521200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6336400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5894100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5976700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5968700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6581200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6394100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6372800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6498200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6545300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5900700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5661200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5656900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5757500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5474000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4802700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4801200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4579800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4244200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4401500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5650300</v>
+      </c>
+      <c r="E61" s="3">
         <v>5196800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5237900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5385700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5359100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5288300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5201000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5179200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4345800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4100100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4530900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3882900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3848700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3938500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3076800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3231700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3304200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3387900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2409400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2432500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2473000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2458000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2516600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2700600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2727900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2726400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2802100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2795900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2871100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2389200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2432100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2463500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2490600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2564100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2550000</v>
-      </c>
-      <c r="AL61" s="3">
-        <v>550000</v>
       </c>
       <c r="AM61" s="3">
         <v>550000</v>
@@ -6623,132 +6766,138 @@
         <v>550000</v>
       </c>
       <c r="AP61" s="3">
+        <v>550000</v>
+      </c>
+      <c r="AQ61" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>717300</v>
+      </c>
+      <c r="E62" s="3">
         <v>737300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>724400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>470100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>487200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>531500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>544100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>539100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>505600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>507500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>536200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>527800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>511800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>521800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1928000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1972100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1986500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2028100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1857900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1808500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1846700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1813100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1811500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1763400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1696400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1720700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1754000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1679800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1582200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1563100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>878200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>869400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>856700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>876400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>924200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>751400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>759600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>804600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>857900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>712500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16514500</v>
+      </c>
+      <c r="E66" s="3">
         <v>16484400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16355200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15889700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15712100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15352600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14930900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15549000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14313300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13919300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13551500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12820600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12855800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12967900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12705000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12712600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12597600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12677600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10861400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10791800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10852100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10619000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10235400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10461400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10414700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11048700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10970900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10871000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10974100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10519600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9232600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9046100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9054600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9249300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9000200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6116000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6124000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5947900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5665700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>5427200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4692100</v>
+      </c>
+      <c r="E72" s="3">
         <v>4611000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4568800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5509800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5426900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5315300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5263800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5306800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5256500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5137600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5065300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4969500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4788900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4644800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4541600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4465600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4329100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4132900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4086300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3995500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3982200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4086000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3979800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3923100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3809600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4487900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4571900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4674900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4630500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4517400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4341200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4349000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4236400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4114500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4050000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4042400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4001100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3964200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4001700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3984000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4526000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4475400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4423000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4786600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4702900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4449900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4337400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4696500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4540600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4402400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4401000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4186100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4071200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3926200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3790400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3664500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3640600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3595700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3490700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3183200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3233900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3324600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3204800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3014100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2849300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3402700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3674700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3642200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3665300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3550900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3450500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3611100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3512000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3510100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3412200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3378200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3288100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3219000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3193700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3322200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E81" s="3">
         <v>188500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-609500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>226200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>254900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>194400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>133100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>226600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>295500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>248900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>316900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>351200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>344500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>304000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>252000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>312400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>372500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>245800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>256000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>228600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>196500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>217700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>171200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>227500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-564400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>136500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>227500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>224400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>160300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>186700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>220200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>176600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>108200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>158400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>190000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>160200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>152500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>185300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>85200</v>
+      </c>
+      <c r="E83" s="3">
         <v>78600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>74200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>64500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>56500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>54800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>50200</v>
       </c>
       <c r="K83" s="3">
         <v>50200</v>
       </c>
       <c r="L83" s="3">
+        <v>50200</v>
+      </c>
+      <c r="M83" s="3">
         <v>48100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>49300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>47100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>46300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>47700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>88000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>86600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>85900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>87400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>72600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>72100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>74000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>72300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>69800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>69100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>63500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>70400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>73200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>68900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>66200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>62000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>63700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>61100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>58500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>58400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>50100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>40300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>39200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>38100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>39200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>37700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400200</v>
+      </c>
+      <c r="E89" s="3">
         <v>63900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>380100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>341600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>209900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-40800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>155000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>484300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>293600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>318300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>353200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>625400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>259500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>197500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>222400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>453600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>392200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>398800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>250100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>303800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>403500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>300900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>579100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>488100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>878300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>74100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>146800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>443800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>239600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>61700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>219600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>470500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>316700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>138400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>272700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>197100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>243500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>101800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>204700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>210900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-107800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-97600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-119400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-101600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-129000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-119800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-181700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-126300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-143600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-115700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-162800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-144500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-117200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-88100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-95600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-91000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-74900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-78000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-127900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-48200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-41600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-48400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-48100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-35400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-101600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-74100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-45600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-140500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-26800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-59600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-43100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-29300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-36900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-135100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-92900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-223600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-170000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-163100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-154800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-262300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-483200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-583600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-178400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-232400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-247300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-180900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-45200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-113500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-122500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1420900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-266300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-88500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-110700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-40700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-47200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-69900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>324200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-35500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-171800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>72600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-184000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-250200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-98200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-70200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1243700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-92200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-163300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-131000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-141800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-97000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,73 +10455,74 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>146200</v>
+      </c>
+      <c r="E96" s="3">
         <v>141700</v>
-      </c>
-      <c r="E96" s="3">
-        <v>143300</v>
       </c>
       <c r="F96" s="3">
         <v>143300</v>
       </c>
       <c r="G96" s="3">
+        <v>143300</v>
+      </c>
+      <c r="H96" s="3">
         <v>143000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>134400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>143500</v>
-      </c>
-      <c r="J96" s="3">
-        <v>139400</v>
       </c>
       <c r="K96" s="3">
         <v>139400</v>
       </c>
       <c r="L96" s="3">
+        <v>139400</v>
+      </c>
+      <c r="M96" s="3">
         <v>132600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>133300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>133500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>133700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>126200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-126400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-126700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-126900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-115900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-116400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-117700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-117600</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-114000</v>
       </c>
       <c r="Y96" s="3">
         <v>-114000</v>
@@ -10297,55 +10531,58 @@
         <v>-114000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-110900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-110800</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-111400</v>
       </c>
       <c r="AE96" s="3">
         <v>-111400</v>
       </c>
       <c r="AF96" s="3">
+        <v>-111400</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-105400</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-105700</v>
       </c>
       <c r="AH96" s="3">
         <v>-105700</v>
       </c>
       <c r="AI96" s="3">
+        <v>-105700</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-105600</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-99000</v>
       </c>
       <c r="AK96" s="3">
         <v>-99000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-99100</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-97600</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-98000</v>
       </c>
       <c r="AP96" s="3">
         <v>-98000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-98000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-180900</v>
+      </c>
+      <c r="E100" s="3">
         <v>56700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-115500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-196200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-26200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>128700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-458800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>507200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-207100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-175200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>306900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-241300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-199900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-157800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-180900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-198500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-329500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>914000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-170800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-270500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-432200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-116000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-484600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-501900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-580800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>53500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-618600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>243500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>145700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>13200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-366200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-200400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-55500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1073700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-102800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-57700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-41200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-38200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-122800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E101" s="3">
         <v>7400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-32100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>14500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>19700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>10100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-31600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-31900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>10100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-31600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-31900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-17400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-13000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>42700</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>7600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2500</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-8200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>4800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>2800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>5500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E102" s="3">
         <v>22800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>45800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-26600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>37500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-59500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-598100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>522800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-494300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-52400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>447400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>124500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-121100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>24300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>110100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-91600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-103900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-204400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-68300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-130600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>127800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>90000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-83600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>629300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>77500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-174300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-111300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>205600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>23400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-25600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>29200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>11100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>104800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>6900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>25200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-65000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>17700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-8500</v>
       </c>
     </row>
